--- a/OMOP Analysis/Results/Output_yearly_costs_OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_yearly_costs_OMOP.xlsx
@@ -402,25 +402,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>445.97</v>
+        <v>568.3</v>
       </c>
       <c r="C2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D2">
-        <v>3650.26</v>
+        <v>9656.440000000001</v>
       </c>
       <c r="E2">
-        <v>420.31</v>
+        <v>516.3</v>
       </c>
       <c r="F2">
-        <v>320.83</v>
+        <v>420</v>
       </c>
       <c r="G2">
-        <v>168</v>
+        <v>210</v>
       </c>
       <c r="H2">
-        <v>588</v>
+        <v>756</v>
       </c>
     </row>
     <row r="3">
@@ -428,25 +428,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>491.91</v>
+        <v>254.24</v>
       </c>
       <c r="C3">
         <v>3</v>
       </c>
       <c r="D3">
-        <v>7049.25</v>
+        <v>3101.25</v>
       </c>
       <c r="E3">
-        <v>451.53</v>
+        <v>242.38</v>
       </c>
       <c r="F3">
-        <v>374.24</v>
+        <v>189</v>
       </c>
       <c r="G3">
-        <v>189</v>
+        <v>84</v>
       </c>
       <c r="H3">
-        <v>655.1900000000001</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>
@@ -506,25 +506,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>425.09</v>
+        <v>548.97</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>3650.26</v>
+        <v>9656.440000000001</v>
       </c>
       <c r="E2">
-        <v>421.03</v>
+        <v>517.8</v>
       </c>
       <c r="F2">
-        <v>294</v>
+        <v>420</v>
       </c>
       <c r="G2">
-        <v>129.94</v>
+        <v>210</v>
       </c>
       <c r="H2">
-        <v>562.5</v>
+        <v>740.75</v>
       </c>
     </row>
     <row r="3">
@@ -532,25 +532,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>479.99</v>
+        <v>244.72</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>7049.25</v>
+        <v>3101.25</v>
       </c>
       <c r="E3">
-        <v>452.39</v>
+        <v>242.65</v>
       </c>
       <c r="F3">
-        <v>357.09</v>
+        <v>180.08</v>
       </c>
       <c r="G3">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="H3">
-        <v>649.2</v>
+        <v>332.39</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_yearly_costs_OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_yearly_costs_OMOP.xlsx
@@ -402,25 +402,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>568.3</v>
+        <v>722.9400000000001</v>
       </c>
       <c r="C2">
         <v>6</v>
       </c>
       <c r="D2">
-        <v>9656.440000000001</v>
+        <v>9614.440000000001</v>
       </c>
       <c r="E2">
-        <v>516.3</v>
+        <v>689.15</v>
       </c>
       <c r="F2">
-        <v>420</v>
+        <v>535.1799999999999</v>
       </c>
       <c r="G2">
-        <v>210</v>
+        <v>278.92</v>
       </c>
       <c r="H2">
-        <v>756</v>
+        <v>943.2</v>
       </c>
     </row>
     <row r="3">
@@ -428,25 +428,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>254.24</v>
+        <v>573.95</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>6.01</v>
       </c>
       <c r="D3">
-        <v>3101.25</v>
+        <v>6217.3</v>
       </c>
       <c r="E3">
-        <v>242.38</v>
+        <v>571.26</v>
       </c>
       <c r="F3">
-        <v>189</v>
+        <v>416.81</v>
       </c>
       <c r="G3">
-        <v>84</v>
+        <v>199.99</v>
       </c>
       <c r="H3">
-        <v>336</v>
+        <v>757.04</v>
       </c>
     </row>
   </sheetData>
@@ -506,25 +506,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>548.97</v>
+        <v>697.17</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>9656.440000000001</v>
+        <v>9614.440000000001</v>
       </c>
       <c r="E2">
-        <v>517.8</v>
+        <v>689.9</v>
       </c>
       <c r="F2">
-        <v>420</v>
+        <v>504</v>
       </c>
       <c r="G2">
-        <v>210</v>
+        <v>252</v>
       </c>
       <c r="H2">
-        <v>740.75</v>
+        <v>924</v>
       </c>
     </row>
     <row r="3">
@@ -532,25 +532,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>244.72</v>
+        <v>553.59</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>3101.25</v>
+        <v>6217.3</v>
       </c>
       <c r="E3">
-        <v>242.65</v>
+        <v>570.99</v>
       </c>
       <c r="F3">
-        <v>180.08</v>
+        <v>390.02</v>
       </c>
       <c r="G3">
-        <v>84</v>
+        <v>168.23</v>
       </c>
       <c r="H3">
-        <v>332.39</v>
+        <v>735.36</v>
       </c>
     </row>
   </sheetData>

--- a/OMOP Analysis/Results/Output_yearly_costs_OMOP.xlsx
+++ b/OMOP Analysis/Results/Output_yearly_costs_OMOP.xlsx
@@ -402,7 +402,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>722.9400000000001</v>
+        <v>777.71</v>
       </c>
       <c r="C2">
         <v>6</v>
@@ -411,16 +411,16 @@
         <v>9614.440000000001</v>
       </c>
       <c r="E2">
-        <v>689.15</v>
+        <v>731.3200000000001</v>
       </c>
       <c r="F2">
-        <v>535.1799999999999</v>
+        <v>583.45</v>
       </c>
       <c r="G2">
-        <v>278.92</v>
+        <v>294</v>
       </c>
       <c r="H2">
-        <v>943.2</v>
+        <v>1013.05</v>
       </c>
     </row>
     <row r="3">
@@ -428,25 +428,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>573.95</v>
+        <v>614.97</v>
       </c>
       <c r="C3">
         <v>6.01</v>
       </c>
       <c r="D3">
-        <v>6217.3</v>
+        <v>7116.73</v>
       </c>
       <c r="E3">
-        <v>571.26</v>
+        <v>603.72</v>
       </c>
       <c r="F3">
-        <v>416.81</v>
+        <v>439.8</v>
       </c>
       <c r="G3">
-        <v>199.99</v>
+        <v>210.29</v>
       </c>
       <c r="H3">
-        <v>757.04</v>
+        <v>807.7</v>
       </c>
     </row>
   </sheetData>
@@ -506,7 +506,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>697.17</v>
+        <v>753.9299999999999</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -515,16 +515,16 @@
         <v>9614.440000000001</v>
       </c>
       <c r="E2">
-        <v>689.9</v>
+        <v>732.39</v>
       </c>
       <c r="F2">
-        <v>504</v>
+        <v>554.37</v>
       </c>
       <c r="G2">
-        <v>252</v>
+        <v>281.5</v>
       </c>
       <c r="H2">
-        <v>924</v>
+        <v>998.75</v>
       </c>
     </row>
     <row r="3">
@@ -532,25 +532,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>553.59</v>
+        <v>596.72</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>6217.3</v>
+        <v>7116.73</v>
       </c>
       <c r="E3">
-        <v>570.99</v>
+        <v>603.78</v>
       </c>
       <c r="F3">
-        <v>390.02</v>
+        <v>420.58</v>
       </c>
       <c r="G3">
-        <v>168.23</v>
+        <v>195.04</v>
       </c>
       <c r="H3">
-        <v>735.36</v>
+        <v>799.09</v>
       </c>
     </row>
   </sheetData>
